--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q40_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009394610407498146</v>
+        <v>0.008581001533106746</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009394610407498146</v>
+        <v>0.008581001533106746</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.008717146343649234</v>
+        <v>0.00787721159958363</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008717146343649234</v>
+        <v>0.00787721159958363</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01053432475292958</v>
+        <v>0.009664112532675118</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01053432475292958</v>
+        <v>0.009664112532675118</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01661164743896898</v>
+        <v>0.01546720649520843</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01661164743896898</v>
+        <v>0.01546720649520843</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02537629522576847</v>
+        <v>0.02364964909027194</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02537629522576847</v>
+        <v>0.02364964909027194</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03455430592206567</v>
+        <v>0.03203946406407775</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03455430592206567</v>
+        <v>0.03203946406407775</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04674885112428217</v>
+        <v>0.04336373091478554</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04674885112428217</v>
+        <v>0.04336373091478554</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05848278481201754</v>
+        <v>0.05438916669654335</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05848278481201754</v>
+        <v>0.05438916669654335</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06675650746993149</v>
+        <v>0.06214290034224112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06675650746993149</v>
+        <v>0.06214290034224112</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07073175945591223</v>
+        <v>0.06578292958022582</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07073175945591223</v>
+        <v>0.06578292958022582</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.07038059132224801</v>
+        <v>0.06535981892177462</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07038059132224801</v>
+        <v>0.06535981892177462</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06808019923350393</v>
+        <v>0.06318521572934623</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06808019923350393</v>
+        <v>0.06318521572934623</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06503580571527748</v>
+        <v>0.06038968769900319</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06503580571527748</v>
+        <v>0.06038968769900319</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06057549368209479</v>
+        <v>0.0562736272992469</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06057549368209479</v>
+        <v>0.0562736272992469</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05932369445968921</v>
+        <v>0.05515284361474842</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05932369445968921</v>
+        <v>0.05515284361474842</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05560962451707503</v>
+        <v>0.05173911363592442</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05560962451707503</v>
+        <v>0.05173911363592442</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05333429455284672</v>
+        <v>0.04966210075763591</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05333429455284672</v>
+        <v>0.04966210075763591</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05471541596844606</v>
+        <v>0.05098354777673507</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05471541596844606</v>
+        <v>0.05098354777673507</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05127505097854892</v>
+        <v>0.0478305076564141</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05127505097854892</v>
+        <v>0.0478305076564141</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05003561905649714</v>
+        <v>0.04669534230691131</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05003561905649714</v>
+        <v>0.04669534230691131</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
